--- a/safety_inspection_forms/041_laboratory_safety_compliance_declaration_form--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/041_laboratory_safety_compliance_declaration_form--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fire_exinguishable_chemical_bib</t>
+          <t>fire exinguishable chemical bib</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fire_extinguisher</t>
+          <t>fire extinguisher</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fire_alarm</t>
+          <t>fire alarm</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lab_cohort</t>
+          <t>lab cohort</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lab_gloves</t>
+          <t>lab gloves</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lab_goggles</t>
+          <t>lab goggles</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fire_extinguisher</t>
+          <t>fire extinguisher</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fire_alarm</t>
+          <t>fire alarm</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fume_hood</t>
+          <t>fume hood</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>safety_shutter</t>
+          <t>safety shutter</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>safety_glass</t>
+          <t>safety glass</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fume_hood</t>
+          <t>fume hood</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>safety_shutter</t>
+          <t>safety shutter</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>safety_glass</t>
+          <t>safety glass</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>gas_cylinder</t>
+          <t>gas cylinder</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>gas_valve</t>
+          <t>gas valve</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>gas_valve</t>
+          <t>gas valve</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>gas_tank</t>
+          <t>gas tank</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>grounded_outlet</t>
+          <t>grounded outlet</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>grounded_system</t>
+          <t>grounded system</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ground_system</t>
+          <t>ground system</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>grounded_box</t>
+          <t>grounded box</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ground_box</t>
+          <t>ground box</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>grounded_wire</t>
+          <t>grounded wire</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ground_wire</t>
+          <t>ground wire</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>grounded_device</t>
+          <t>grounded device</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ground_device</t>
+          <t>ground device</t>
         </is>
       </c>
     </row>
